--- a/Data/Ganapathy Residence Expense.xlsx
+++ b/Data/Ganapathy Residence Expense.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d772b42a7a1256b2/Desktop/Business/TSK Constructions/Projects/Building Construction/Ganapathy Residence @ VSN Garden/Accounts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="978" documentId="13_ncr:1_{214A6028-1054-4F6B-A253-454EBD54C90F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37045FD1-73F4-41A0-AA37-6F51CD88EF38}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{1A79EF5D-F023-45A9-8CBF-78AD93EE0640}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D7C898F-75A9-4344-A696-2C8821ACA078}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="Detail1" sheetId="7" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Expenses!$A$1:$D$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Expenses!$A$1:$D$94</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="132">
   <si>
     <t>DATE</t>
   </si>
@@ -386,6 +386,60 @@
   </si>
   <si>
     <t>RSK part amount</t>
+  </si>
+  <si>
+    <t>Mason lab Adv</t>
+  </si>
+  <si>
+    <t>Lab tea</t>
+  </si>
+  <si>
+    <t>Mani Lab Payment</t>
+  </si>
+  <si>
+    <t>SCAFFOLDING</t>
+  </si>
+  <si>
+    <t>Scaffolding Advance</t>
+  </si>
+  <si>
+    <t>Advance</t>
+  </si>
+  <si>
+    <t>Tank Shifting Selvam</t>
+  </si>
+  <si>
+    <t>Lab Adv</t>
+  </si>
+  <si>
+    <t>Azhagiri Mason Lab</t>
+  </si>
+  <si>
+    <t>Pending Amt</t>
+  </si>
+  <si>
+    <t>Auto Dr site to VSN</t>
+  </si>
+  <si>
+    <t>Madhappan Lab Payment</t>
+  </si>
+  <si>
+    <t>Madhappan Extra</t>
+  </si>
+  <si>
+    <t>Chakra Payment</t>
+  </si>
+  <si>
+    <t>Ramdev Part Amt</t>
+  </si>
+  <si>
+    <t>Mason Advance Azagiri</t>
+  </si>
+  <si>
+    <t>Madhappan Xtra</t>
+  </si>
+  <si>
+    <t>Terrace floor Grill steps adv</t>
   </si>
 </sst>
 </file>
@@ -455,7 +509,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -478,22 +532,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -525,10 +568,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -641,18 +680,14 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="TAMIL" refreshedDate="46122.450627777776" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="245" xr:uid="{ECDDBE9B-8132-48D6-AEC8-4A5EB49DBA77}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="TAMIL" refreshedDate="46157.674854745368" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="245" xr:uid="{ECDDBE9B-8132-48D6-AEC8-4A5EB49DBA77}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:D1006" sheet="Expenses"/>
   </cacheSource>
   <cacheFields count="4">
     <cacheField name="DATE" numFmtId="164">
-      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2026-01-28T00:00:00" maxDate="2026-04-10T00:00:00"/>
+      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2026-01-28T00:00:00" maxDate="2026-05-15T00:00:00"/>
     </cacheField>
     <cacheField name="TYPE OF EXPENSE" numFmtId="0">
       <sharedItems containsBlank="1" count="27">
@@ -672,6 +707,7 @@
         <s v="DIESEL"/>
         <s v="CARPENTER LABOUR"/>
         <s v="SALARY"/>
+        <s v="FABRICATON WORK"/>
         <m/>
         <s v="LABOUR TRANSPORT" u="1"/>
         <s v="MASON MATERIALS" u="1"/>
@@ -680,7 +716,6 @@
         <s v="RO WATER" u="1"/>
         <s v="SALT WATER" u="1"/>
         <s v="ELECTRICIAL LABOUR" u="1"/>
-        <s v="FABRICATON WORK" u="1"/>
         <s v="RENTAL TRANSPORT" u="1"/>
         <s v="PETROL-GENSET" u="1"/>
       </sharedItems>
@@ -1021,1154 +1056,1154 @@
     <s v="Clamp nails for nilavu fixing - Nithish"/>
   </r>
   <r>
-    <m/>
+    <d v="2026-04-11T00:00:00"/>
+    <x v="2"/>
+    <n v="19350"/>
+    <s v="Rajkumar lab payment"/>
+  </r>
+  <r>
+    <d v="2026-04-11T00:00:00"/>
+    <x v="4"/>
+    <n v="17850"/>
+    <s v="Fitter lab payment"/>
+  </r>
+  <r>
+    <d v="2026-04-11T00:00:00"/>
+    <x v="0"/>
+    <n v="100000"/>
+    <s v="AK Steels Payment"/>
+  </r>
+  <r>
+    <d v="2026-04-13T00:00:00"/>
+    <x v="6"/>
+    <n v="855"/>
+    <s v="Lab Tea"/>
+  </r>
+  <r>
+    <d v="2026-04-13T00:00:00"/>
+    <x v="7"/>
+    <n v="1060"/>
+    <s v="Nails for Roof"/>
+  </r>
+  <r>
+    <d v="2026-04-15T00:00:00"/>
+    <x v="2"/>
+    <n v="5000"/>
+    <s v="Rajkumar lab adv"/>
+  </r>
+  <r>
+    <d v="2026-04-15T00:00:00"/>
+    <x v="13"/>
+    <n v="2000"/>
+    <s v="Car Diesel"/>
+  </r>
+  <r>
+    <d v="2026-04-16T00:00:00"/>
+    <x v="3"/>
+    <n v="1510"/>
+    <s v="Column box"/>
+  </r>
+  <r>
+    <d v="2026-04-17T00:00:00"/>
+    <x v="5"/>
+    <n v="1500"/>
+    <s v="Cement Transfer from Happy Town Nithish"/>
+  </r>
+  <r>
+    <d v="2026-04-17T00:00:00"/>
+    <x v="11"/>
+    <n v="180"/>
+    <s v="Concrete Machine Diesel Nithish"/>
+  </r>
+  <r>
+    <d v="2026-04-17T00:00:00"/>
+    <x v="6"/>
+    <n v="676"/>
+    <s v="Lab Tea"/>
+  </r>
+  <r>
+    <d v="2026-04-18T00:00:00"/>
+    <x v="2"/>
+    <n v="24300"/>
+    <s v="Rajkumar lab payment"/>
+  </r>
+  <r>
+    <d v="2026-04-18T00:00:00"/>
+    <x v="14"/>
+    <n v="15000"/>
+    <s v="Labour Advance"/>
+  </r>
+  <r>
+    <d v="2026-04-18T00:00:00"/>
+    <x v="12"/>
+    <n v="14500"/>
+    <s v="Second floor Roof concrete"/>
+  </r>
+  <r>
+    <d v="2026-04-18T00:00:00"/>
+    <x v="4"/>
+    <n v="13250"/>
+    <s v="Fitter lab Payment"/>
+  </r>
+  <r>
+    <d v="2026-04-18T00:00:00"/>
+    <x v="4"/>
+    <n v="250"/>
+    <s v="Kannan Xtra"/>
+  </r>
+  <r>
+    <d v="2026-04-18T00:00:00"/>
+    <x v="4"/>
+    <n v="550"/>
+    <s v="Kannan Xtra"/>
+  </r>
+  <r>
+    <d v="2026-04-18T00:00:00"/>
+    <x v="10"/>
+    <n v="3000"/>
+    <s v="1000 Roof conc 2000 gaudi work"/>
+  </r>
+  <r>
+    <d v="2026-04-18T00:00:00"/>
     <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <m/>
-    <x v="16"/>
+    <n v="14000"/>
+    <s v="Window grill Payment"/>
+  </r>
+  <r>
+    <d v="2026-04-24T00:00:00"/>
+    <x v="6"/>
+    <n v="927"/>
+    <s v="Tea Lab"/>
+  </r>
+  <r>
+    <d v="2026-04-25T00:00:00"/>
+    <x v="2"/>
+    <n v="25800"/>
+    <s v="Mason Lab Payment"/>
+  </r>
+  <r>
+    <d v="2026-04-25T00:00:00"/>
+    <x v="10"/>
+    <n v="1000"/>
+    <s v="Selvam FF pipe work"/>
+  </r>
+  <r>
+    <d v="2026-04-25T00:00:00"/>
+    <x v="0"/>
+    <n v="2300"/>
+    <s v="Electrical Pipe Purchase by Selvam"/>
+  </r>
+  <r>
+    <d v="2026-05-02T00:00:00"/>
+    <x v="2"/>
+    <n v="13150"/>
+    <s v="Mason Lab Payment"/>
+  </r>
+  <r>
+    <d v="2026-05-02T00:00:00"/>
+    <x v="0"/>
+    <n v="20000"/>
+    <s v="Palani Murugan Payment"/>
+  </r>
+  <r>
+    <d v="2026-05-02T00:00:00"/>
+    <x v="0"/>
+    <n v="24000"/>
+    <s v="Vel Brick"/>
+  </r>
+  <r>
+    <d v="2026-02-04T00:00:00"/>
+    <x v="14"/>
+    <n v="5000"/>
+    <s v="Nilavu and Window work"/>
+  </r>
+  <r>
+    <d v="2026-05-07T00:00:00"/>
+    <x v="2"/>
+    <n v="2000"/>
+    <s v="Azhagiri Mason Adv"/>
+  </r>
+  <r>
+    <d v="2026-05-07T00:00:00"/>
+    <x v="6"/>
+    <n v="774"/>
+    <s v="Lab Tea"/>
+  </r>
+  <r>
+    <d v="2026-05-09T00:00:00"/>
+    <x v="2"/>
+    <n v="17250"/>
+    <s v="Mason Lab Payment"/>
+  </r>
+  <r>
+    <d v="2026-05-09T00:00:00"/>
+    <x v="10"/>
+    <n v="3000"/>
+    <s v="Selvam Labour"/>
+  </r>
+  <r>
+    <d v="2026-05-09T00:00:00"/>
+    <x v="14"/>
+    <n v="5000"/>
+    <s v="Carpenter Advance"/>
+  </r>
+  <r>
+    <d v="2026-05-09T00:00:00"/>
+    <x v="0"/>
+    <n v="100000"/>
+    <s v="RSK part amount"/>
+  </r>
+  <r>
+    <d v="2026-05-13T00:00:00"/>
+    <x v="2"/>
+    <n v="3000"/>
+    <s v="Mason lab Adv"/>
+  </r>
+  <r>
+    <d v="2026-05-14T00:00:00"/>
+    <x v="6"/>
+    <n v="441"/>
+    <s v="Lab tea"/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
     <m/>
     <m/>
   </r>
@@ -2177,34 +2212,34 @@
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1FC8C9A3-14B4-46FA-8D51-AAF7A0B6E9CA}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Expense">
-  <location ref="A3:B20" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <location ref="A3:B21" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
       <items count="28">
         <item x="0"/>
         <item x="7"/>
+        <item m="1" x="20"/>
         <item m="1" x="19"/>
-        <item m="1" x="18"/>
         <item x="5"/>
         <item m="1" x="26"/>
         <item x="1"/>
-        <item h="1" x="16"/>
+        <item h="1" x="17"/>
         <item x="2"/>
         <item x="4"/>
         <item x="6"/>
         <item x="11"/>
         <item x="12"/>
         <item x="3"/>
-        <item m="1" x="17"/>
-        <item m="1" x="20"/>
+        <item m="1" x="18"/>
+        <item m="1" x="21"/>
         <item m="1" x="25"/>
         <item x="13"/>
         <item x="15"/>
-        <item m="1" x="21"/>
         <item m="1" x="22"/>
         <item m="1" x="23"/>
         <item m="1" x="24"/>
+        <item x="16"/>
         <item x="8"/>
         <item x="9"/>
         <item x="10"/>
@@ -2218,7 +2253,7 @@
   <rowFields count="1">
     <field x="1"/>
   </rowFields>
-  <rowItems count="17">
+  <rowItems count="18">
     <i>
       <x/>
     </i>
@@ -2254,6 +2289,9 @@
     </i>
     <i>
       <x v="18"/>
+    </i>
+    <i>
+      <x v="22"/>
     </i>
     <i>
       <x v="23"/>
@@ -2590,7 +2628,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA8E933-C0E6-4334-87CB-622BD050B00B}">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.08984375" bestFit="1" customWidth="1"/>
@@ -2623,7 +2661,7 @@
       </c>
       <c r="M1" s="8">
         <f>SUM(B2:B100)</f>
-        <v>1400000</v>
+        <v>1800000</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
@@ -2674,6 +2712,23 @@
         <v>18</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="4">
+        <v>46167</v>
+      </c>
+      <c r="B5" s="7">
+        <v>400000</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>45</v>
       </c>
     </row>
@@ -2719,7 +2774,7 @@
       </c>
       <c r="J1" s="7">
         <f>'Payment Received'!M1</f>
-        <v>1400000</v>
+        <v>1800000</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
@@ -2740,7 +2795,7 @@
       </c>
       <c r="J2" s="7">
         <f>SUM(C2:C1000)</f>
-        <v>1307317</v>
+        <v>1580360</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
@@ -2761,7 +2816,7 @@
       </c>
       <c r="J3" s="7">
         <f>J1-J2</f>
-        <v>92683</v>
+        <v>219640</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
@@ -3917,16 +3972,16 @@
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A86" s="28">
+      <c r="A86" s="4">
         <v>46151</v>
       </c>
-      <c r="B86" s="29" t="s">
+      <c r="B86" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C86" s="30">
+      <c r="C86" s="7">
         <v>5000</v>
       </c>
-      <c r="D86" s="29" t="s">
+      <c r="D86" s="1" t="s">
         <v>112</v>
       </c>
     </row>
@@ -3945,137 +4000,313 @@
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A88" s="4"/>
-      <c r="B88" s="1"/>
-      <c r="C88" s="7"/>
-      <c r="D88" s="1"/>
+      <c r="A88" s="4">
+        <v>46155</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C88" s="7">
+        <v>3000</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A89" s="4"/>
-      <c r="B89" s="1"/>
-      <c r="C89" s="7"/>
-      <c r="D89" s="1"/>
+      <c r="A89" s="4">
+        <v>46156</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C89" s="7">
+        <v>441</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A90" s="4"/>
-      <c r="B90" s="1"/>
-      <c r="C90" s="7"/>
-      <c r="D90" s="1"/>
+      <c r="A90" s="4">
+        <v>46158</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C90" s="7">
+        <v>41200</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A91" s="4"/>
-      <c r="B91" s="1"/>
-      <c r="C91" s="7"/>
-      <c r="D91" s="1"/>
+      <c r="A91" s="4">
+        <v>46158</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C91" s="7">
+        <v>10000</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A92" s="4"/>
-      <c r="B92" s="1"/>
-      <c r="C92" s="7"/>
-      <c r="D92" s="1"/>
+      <c r="A92" s="4">
+        <v>46158</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C92" s="7">
+        <v>5000</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A93" s="4"/>
-      <c r="B93" s="1"/>
-      <c r="C93" s="7"/>
-      <c r="D93" s="1"/>
+      <c r="A93" s="4">
+        <v>46158</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C93" s="7">
+        <v>1000</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A94" s="4"/>
-      <c r="B94" s="1"/>
-      <c r="C94" s="7"/>
-      <c r="D94" s="1"/>
+      <c r="A94" s="4">
+        <v>46158</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C94" s="7">
+        <v>225</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A95" s="4"/>
-      <c r="B95" s="1"/>
-      <c r="C95" s="7"/>
-      <c r="D95" s="1"/>
+      <c r="A95" s="4">
+        <v>46162</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C95" s="7">
+        <v>2000</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A96" s="4"/>
-      <c r="B96" s="1"/>
-      <c r="C96" s="7"/>
-      <c r="D96" s="1"/>
+      <c r="A96" s="4">
+        <v>46165</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C96" s="7">
+        <v>24750</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A97" s="4"/>
-      <c r="B97" s="1"/>
-      <c r="C97" s="7"/>
-      <c r="D97" s="1"/>
+      <c r="A97" s="4">
+        <v>46165</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C97" s="7">
+        <v>2600</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A98" s="4"/>
-      <c r="B98" s="1"/>
-      <c r="C98" s="7"/>
-      <c r="D98" s="1"/>
+      <c r="A98" s="4">
+        <v>46165</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C98" s="7">
+        <v>1134</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A99" s="4"/>
-      <c r="B99" s="1"/>
-      <c r="C99" s="7"/>
-      <c r="D99" s="1"/>
+      <c r="A99" s="4">
+        <v>46169</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C99" s="7">
+        <v>5000</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A100" s="4"/>
-      <c r="B100" s="1"/>
-      <c r="C100" s="7"/>
-      <c r="D100" s="1"/>
+      <c r="A100" s="4">
+        <v>46169</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C100" s="7">
+        <v>443</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>124</v>
+      </c>
       <c r="H100" s="8"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A101" s="4"/>
-      <c r="B101" s="1"/>
-      <c r="C101" s="7"/>
-      <c r="D101" s="1"/>
+      <c r="A101" s="4">
+        <v>46172</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C101" s="7">
+        <v>66450</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A102" s="4"/>
-      <c r="B102" s="1"/>
-      <c r="C102" s="7"/>
-      <c r="D102" s="1"/>
+      <c r="A102" s="4">
+        <v>46172</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C102" s="7">
+        <v>500</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A103" s="4"/>
-      <c r="B103" s="1"/>
-      <c r="C103" s="7"/>
-      <c r="D103" s="1"/>
+      <c r="A103" s="4">
+        <v>46172</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C103" s="7">
+        <v>25000</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A104" s="4"/>
-      <c r="B104" s="1"/>
-      <c r="C104" s="7"/>
-      <c r="D104" s="1"/>
+      <c r="A104" s="4">
+        <v>46172</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C104" s="7">
+        <v>14500</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A105" s="4"/>
-      <c r="B105" s="1"/>
-      <c r="C105" s="7"/>
-      <c r="D105" s="1"/>
+      <c r="A105" s="4">
+        <v>46172</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C105" s="7">
+        <v>20000</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A106" s="4"/>
-      <c r="B106" s="1"/>
-      <c r="C106" s="7"/>
-      <c r="D106" s="1"/>
+      <c r="A106" s="4">
+        <v>46176</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C106" s="7">
+        <v>4000</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A107" s="4"/>
-      <c r="B107" s="1"/>
-      <c r="C107" s="7"/>
-      <c r="D107" s="1"/>
+      <c r="A107" s="4">
+        <v>46179</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C107" s="7">
+        <v>35625</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A108" s="4"/>
-      <c r="B108" s="1"/>
-      <c r="C108" s="7"/>
-      <c r="D108" s="1"/>
+      <c r="A108" s="4">
+        <v>46179</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C108" s="7">
+        <v>175</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A109" s="4"/>
-      <c r="B109" s="1"/>
-      <c r="C109" s="7"/>
-      <c r="D109" s="1"/>
+      <c r="A109" s="4">
+        <v>46179</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C109" s="7">
+        <v>10000</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A110" s="4"/>
@@ -4921,7 +5152,7 @@
       <c r="F304" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D42" xr:uid="{E716AC5E-A74E-4151-8738-1C2F14C945B6}"/>
+  <autoFilter ref="A1:D94" xr:uid="{E716AC5E-A74E-4151-8738-1C2F14C945B6}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -4940,7 +5171,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCAE1F4E-AA4E-4ECE-A323-49517B1EF568}">
-  <dimension ref="A1:A27"/>
+  <dimension ref="A1:A28"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.453125" bestFit="1" customWidth="1"/>
@@ -5077,8 +5308,13 @@
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A27" s="27" t="s">
+      <c r="A27" s="1" t="s">
         <v>60</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A28" s="1" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -5088,7 +5324,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAED5D36-3AAD-4012-B629-BC62E5C1A2B7}">
-  <dimension ref="A3:B20"/>
+  <dimension ref="A3:B21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.453125" bestFit="1" customWidth="1"/>
@@ -5108,7 +5344,7 @@
         <v>21</v>
       </c>
       <c r="B4" s="18">
-        <v>251020</v>
+        <v>497320</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -5116,7 +5352,7 @@
         <v>20</v>
       </c>
       <c r="B5" s="18">
-        <v>1370</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -5124,7 +5360,7 @@
         <v>34</v>
       </c>
       <c r="B6" s="18">
-        <v>3100</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
@@ -5140,7 +5376,7 @@
         <v>22</v>
       </c>
       <c r="B8" s="18">
-        <v>117250</v>
+        <v>227100</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -5148,7 +5384,7 @@
         <v>24</v>
       </c>
       <c r="B9" s="18">
-        <v>77950</v>
+        <v>109850</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
@@ -5156,7 +5392,7 @@
         <v>29</v>
       </c>
       <c r="B10" s="18">
-        <v>2585</v>
+        <v>6258</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
@@ -5164,7 +5400,7 @@
         <v>28</v>
       </c>
       <c r="B11" s="18">
-        <v>370</v>
+        <v>550</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
@@ -5172,7 +5408,7 @@
         <v>23</v>
       </c>
       <c r="B12" s="18">
-        <v>12000</v>
+        <v>26500</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
@@ -5180,7 +5416,7 @@
         <v>31</v>
       </c>
       <c r="B13" s="18">
-        <v>4860</v>
+        <v>6370</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
@@ -5188,7 +5424,7 @@
         <v>38</v>
       </c>
       <c r="B14" s="18">
-        <v>2000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
@@ -5201,42 +5437,50 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="14" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="B16" s="18">
-        <v>103000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="14" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="B17" s="18">
-        <v>2500</v>
+        <v>103000</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="14" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="B18" s="18">
-        <v>4500</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="B19" s="18">
+        <v>11500</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="B19" s="18">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" s="9" t="s">
+      <c r="B20" s="18">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="19">
-        <v>852285</v>
+      <c r="B21" s="19">
+        <v>1310758</v>
       </c>
     </row>
   </sheetData>
